--- a/artfynd/A 41222-2025 artfynd.xlsx
+++ b/artfynd/A 41222-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1605,6 +1605,126 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128161046</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jagbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>623562</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6586724</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41222-2025 artfynd.xlsx
+++ b/artfynd/A 41222-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1377604</v>
+        <v>116589</v>
       </c>
       <c r="B2" t="n">
-        <v>86132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4374</v>
+        <v>359</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul vaxskivling</t>
+          <t>Rökfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
+          <t>Clavaria fumosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Wünsche</t>
+          <t>Pers.:Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623606.9867417694</v>
+        <v>623607</v>
       </c>
       <c r="R2" t="n">
-        <v>6586685.536505024</v>
+        <v>6586686</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2012-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1586480</v>
+        <v>1099053</v>
       </c>
       <c r="B3" t="n">
-        <v>86136</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88978</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4379</v>
+        <v>3294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Toppvaxskivling</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Clavulinopsis corniculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Schaeff. : Fr.) Corner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623606.9867417694</v>
+        <v>623607</v>
       </c>
       <c r="R3" t="n">
-        <v>6586685.536505024</v>
+        <v>6586686</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -865,19 +845,9 @@
           <t>2012-09-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1197525</v>
+        <v>1377604</v>
       </c>
       <c r="B4" t="n">
-        <v>86314</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,19 +890,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4392</v>
+        <v>4374</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Hygrocybe chlorophana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623606.9867417694</v>
+        <v>623607</v>
       </c>
       <c r="R4" t="n">
-        <v>6586685.536505024</v>
+        <v>6586686</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -978,19 +947,9 @@
           <t>2012-09-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1624178</v>
+        <v>1452793</v>
       </c>
       <c r="B5" t="n">
-        <v>86148</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4383</v>
+        <v>4377</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Småvaxskivling</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrocybe insipida</t>
+          <t>Hygrocybe coccinea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(J.E.Lange) M.M.Moser</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623606.9867417694</v>
+        <v>623607</v>
       </c>
       <c r="R5" t="n">
-        <v>6586685.536505024</v>
+        <v>6586686</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1095,21 +1049,11 @@
           <t>2012-09-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-09-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1121,7 +1065,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>sandignbetesmark</t>
+          <t>sandig betesmark</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1139,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1636482</v>
+        <v>1586480</v>
       </c>
       <c r="B6" t="n">
-        <v>86105</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4384</v>
+        <v>4379</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grå vaxskivling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gliophorus irrigatus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) A.M.Ainsw. &amp; P.M.Kirk</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623606.9867417694</v>
+        <v>623607</v>
       </c>
       <c r="R6" t="n">
-        <v>6586685.536505024</v>
+        <v>6586686</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1212,19 +1151,9 @@
           <t>2012-09-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2012-09-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,37 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116589</v>
+        <v>1624178</v>
       </c>
       <c r="B7" t="n">
-        <v>84986</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>359</v>
+        <v>4383</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rökfingersvamp</t>
+          <t>Småvaxing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Clavaria fumosa</t>
+          <t>Hygrocybe insipida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pers.:Fr.</t>
+          <t>(J.E.Lange) M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1296,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623606.9867417694</v>
+        <v>623607</v>
       </c>
       <c r="R7" t="n">
-        <v>6586685.536505024</v>
+        <v>6586686</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1329,21 +1253,11 @@
           <t>2012-09-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2012-09-11</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1355,7 +1269,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>sandig betesmark</t>
+          <t>sandignbetesmark</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1373,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1452793</v>
+        <v>1636482</v>
       </c>
       <c r="B8" t="n">
-        <v>86134</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89054</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4377</v>
+        <v>4384</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Gråvaxing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Gliophorus irrigatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Pers.) A.M.Ainsw. &amp; P.M.Kirk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1413,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623606.9867417694</v>
+        <v>623607</v>
       </c>
       <c r="R8" t="n">
-        <v>6586685.536505024</v>
+        <v>6586686</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1446,19 +1355,9 @@
           <t>2012-09-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-09-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1099053</v>
+        <v>1197525</v>
       </c>
       <c r="B9" t="n">
-        <v>85000</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,23 +1400,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3294</v>
+        <v>4392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Ängsvaxing agg.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Schaeff. : Fr.) Corner</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1530,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623606.9867417694</v>
+        <v>623607</v>
       </c>
       <c r="R9" t="n">
-        <v>6586685.536505024</v>
+        <v>6586686</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -1563,19 +1453,9 @@
           <t>2012-09-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2012-09-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128161046</v>
+        <v>125496256</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,36 +1498,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100065</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1655,13 +1530,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623562</v>
+        <v>623474</v>
       </c>
       <c r="R10" t="n">
-        <v>6586724</v>
+        <v>6586809</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,22 +1560,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gärdet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,15 +1595,805 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Johannes (Jan) Neelissen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johannes (Jan) Neelissen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125496258</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57546</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102963</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skrattmås</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chroicocephalus ridibundus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jagbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>623474</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6586809</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johannes (Jan) Neelissen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johannes (Jan) Neelissen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125496264</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jagbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>623474</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6586809</v>
+      </c>
+      <c r="S12" t="n">
+        <v>11</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johannes (Jan) Neelissen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johannes (Jan) Neelissen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>116802425</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jagbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>623727</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6586573</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125496276</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jagbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>623474</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6586809</v>
+      </c>
+      <c r="S14" t="n">
+        <v>11</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johannes (Jan) Neelissen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johannes (Jan) Neelissen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128161046</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jagbacken, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>623562</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6586724</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Michael Lander</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Michael Lander</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>108638327</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57572</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205660</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Silltrut</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Larus fuscus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Eneby, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>623525</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6586529</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Björn Carlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>79740622</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Eneby, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>623502</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6586596</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-08-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-08-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sarah J Leander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sarah J Leander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41222-2025 artfynd.xlsx
+++ b/artfynd/A 41222-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116589</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1099053</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1377604</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1452793</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1586480</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1624178</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1636482</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1197525</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125496256</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125496258</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1834,6 +1889,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125496264</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1940,6 +2000,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116802425</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2055,6 +2120,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125496276</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128161046</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108638327</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2394,8 +2474,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79740622</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>